--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -106,9 +106,6 @@
     <t>SANTOS</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
@@ -136,30 +133,27 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>GALICIA</t>
   </si>
   <si>
@@ -175,12 +169,6 @@
     <t>TELLEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
     <t>HAZEL</t>
   </si>
   <si>
@@ -202,9 +190,6 @@
     <t>AZUL MARIAM</t>
   </si>
   <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
@@ -233,12 +218,6 @@
   </si>
   <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
   </si>
 </sst>
 </file>
@@ -743,19 +722,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -929,7 +908,7 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1115,19 +1094,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1163,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1201,10 +1180,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1224,10 +1203,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1247,10 +1226,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1270,10 +1249,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1293,10 +1272,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1316,10 +1295,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1339,10 +1318,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1356,22 +1335,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920111</v>
+        <v>21330051920145</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1379,16 +1358,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920145</v>
+        <v>21330051920148</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1402,45 +1381,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920148</v>
+        <v>22330051920221</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920221</v>
+        <v>22330051920404</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1448,16 +1427,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920404</v>
+        <v>22330051920274</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1471,16 +1450,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920274</v>
+        <v>22330051920287</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1494,22 +1473,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920287</v>
+        <v>22330051920291</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1517,16 +1496,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920291</v>
+        <v>22330051920295</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1540,16 +1519,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920295</v>
+        <v>22330051920298</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1563,16 +1542,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920298</v>
+        <v>22330051920408</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1581,75 +1560,6 @@
         <v>13</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920408</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920122</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>18330051920377</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -85,42 +85,45 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -133,12 +136,30 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>CASASOLA</t>
   </si>
   <si>
@@ -148,76 +169,67 @@
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>TELLEZ</t>
   </si>
   <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>MARIELA</t>
+  </si>
+  <si>
+    <t>ARAWY</t>
+  </si>
+  <si>
     <t>HAZEL</t>
   </si>
   <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
   </si>
   <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
     <t>ALDO</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>DULCE REGINA</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -667,22 +679,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>27</v>
       </c>
       <c r="G4">
-        <v>65.84999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,13 +868,13 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1039,22 +1051,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>27</v>
       </c>
       <c r="G4">
-        <v>65.84999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1142,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1174,22 +1186,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920368</v>
+        <v>22330051920213</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1197,22 +1209,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1220,16 +1232,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920265</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1243,22 +1255,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920272</v>
+        <v>22330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1266,22 +1278,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920281</v>
+        <v>21330051920148</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1289,114 +1301,114 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920417</v>
+        <v>22330051920221</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920397</v>
+        <v>22330051920421</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920145</v>
+        <v>22330051920368</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920148</v>
+        <v>22330051920256</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920221</v>
+        <v>21330051920396</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1407,13 +1419,13 @@
         <v>22330051920404</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1427,16 +1439,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920274</v>
+        <v>22330051920265</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1450,16 +1462,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920287</v>
+        <v>22330051920272</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1473,22 +1485,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920291</v>
+        <v>22330051920274</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1496,16 +1508,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920295</v>
+        <v>22330051920291</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1519,16 +1531,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920298</v>
+        <v>22330051920295</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1542,16 +1554,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920408</v>
+        <v>22330051920298</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1560,6 +1572,52 @@
         <v>13</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920408</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920145</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -85,99 +85,108 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
     <t>AILYN</t>
   </si>
   <si>
@@ -187,6 +196,9 @@
     <t>AZUL MARIAM</t>
   </si>
   <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
     <t>ROGELIO</t>
   </si>
   <si>
@@ -227,6 +239,12 @@
   </si>
   <si>
     <t>DIEGO</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
   </si>
   <si>
     <t>ALEXIS ISAI</t>
@@ -917,16 +935,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>61.54</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -940,16 +961,19 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>46.67</v>
+      </c>
+      <c r="H7">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1109,16 +1133,16 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>84.62</v>
+        <v>61.54</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1144,7 +1168,7 @@
         <v>46.67</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,22 +1210,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920213</v>
+        <v>22330051920366</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1209,22 +1233,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>22330051920279</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1232,22 +1256,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920279</v>
+        <v>22330051920397</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1255,22 +1279,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920397</v>
+        <v>21330051920117</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1284,10 +1308,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1310,7 +1334,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1330,10 +1354,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1353,10 +1377,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1376,10 +1400,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1399,10 +1423,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1422,10 +1446,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1445,10 +1469,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1468,10 +1492,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1494,7 +1518,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1514,10 +1538,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1537,10 +1561,10 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1563,7 +1587,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1583,10 +1607,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1600,24 +1624,70 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920145</v>
+        <v>21330051920130</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>18330051920377</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920145</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
         <v>15</v>
       </c>
-      <c r="G20">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -88,166 +88,166 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
     <t>ENCARNACION</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
     <t>JOSE</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>AILYN</t>
   </si>
   <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
     <t>AZUL MARIAM</t>
   </si>
   <si>
     <t>DIANA IRAIS</t>
   </si>
   <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>MARIELA</t>
+  </si>
+  <si>
+    <t>ARAWY</t>
+  </si>
+  <si>
+    <t>HAZEL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
-    <t>HAZEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1216,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -1256,13 +1256,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920397</v>
+        <v>22330051920291</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>58</v>
@@ -1279,22 +1279,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920117</v>
+        <v>22330051920397</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
         <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920148</v>
+        <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1317,7 +1317,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1325,36 +1325,36 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920221</v>
+        <v>21330051920145</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920421</v>
+        <v>22330051920221</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
         <v>62</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920368</v>
+        <v>22330051920421</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1386,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920256</v>
+        <v>22330051920368</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920396</v>
+        <v>22330051920256</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -1432,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920404</v>
+        <v>21330051920396</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920265</v>
+        <v>22330051920404</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920272</v>
+        <v>22330051920265</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -1509,13 +1509,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920274</v>
+        <v>22330051920272</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>69</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920291</v>
+        <v>22330051920274</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
         <v>70</v>
@@ -1547,7 +1547,7 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>22330051920295</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -1581,10 +1581,10 @@
         <v>22330051920298</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
         <v>72</v>
@@ -1604,7 +1604,7 @@
         <v>22330051920408</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
         <v>52</v>
@@ -1627,7 +1627,7 @@
         <v>21330051920130</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>53</v>
@@ -1650,7 +1650,7 @@
         <v>18330051920377</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
         <v>54</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920145</v>
+        <v>21330051920148</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
         <v>55</v>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -85,28 +85,52 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
     <t>RONZON</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>TEPOLE</t>
@@ -115,18 +139,9 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>ELIZALDE</t>
   </si>
   <si>
@@ -139,22 +154,43 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>TETLACTLE</t>
@@ -163,18 +199,12 @@
     <t>SOTO</t>
   </si>
   <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
     <t>CASASOLA</t>
   </si>
   <si>
     <t>GALLARDO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>TELLEZ</t>
   </si>
   <si>
@@ -187,31 +217,58 @@
     <t>GALICIA</t>
   </si>
   <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
     <t>AILYN</t>
   </si>
   <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>EFRAIN DE JESUS</t>
   </si>
   <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>AZUL MARIAM</t>
   </si>
   <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
     <t>DIANA IRAIS</t>
   </si>
   <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
-    <t>MARIELA</t>
+    <t>JESUS ALEJANDRO</t>
   </si>
   <si>
     <t>ARAWY</t>
   </si>
   <si>
-    <t>HAZEL</t>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
   </si>
   <si>
     <t>JONATHAN</t>
@@ -220,9 +277,6 @@
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
@@ -232,13 +286,7 @@
     <t>AGUSTIN ARTURO</t>
   </si>
   <si>
-    <t>GAEL</t>
-  </si>
-  <si>
     <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
   <si>
     <t>EDWIN YAMIL</t>
@@ -843,16 +891,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70.59</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -866,16 +917,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>65.84999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -912,16 +966,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>61.11</v>
+      </c>
+      <c r="H5">
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1029,16 +1086,16 @@
         <v>4</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1055,13 +1112,13 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>75.61</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -1107,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>61.11</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1178,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1210,22 +1267,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920366</v>
+        <v>22330051920216</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1233,22 +1290,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920279</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1256,22 +1313,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920291</v>
+        <v>22330051920404</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1279,22 +1336,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920397</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1302,22 +1359,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920117</v>
+        <v>22330051920291</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1325,22 +1382,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920145</v>
+        <v>22330051920412</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1348,183 +1405,183 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920221</v>
+        <v>22330051920307</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920421</v>
+        <v>22330051920419</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920368</v>
+        <v>22330051920308</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920256</v>
+        <v>22330051920397</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920396</v>
+        <v>22330051920314</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920404</v>
+        <v>21330051920117</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920265</v>
+        <v>21330051920145</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920272</v>
+        <v>22330051920317</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1532,22 +1589,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920274</v>
+        <v>22330051920421</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1555,22 +1612,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920295</v>
+        <v>22330051920238</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1578,22 +1635,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920298</v>
+        <v>22330051920242</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1601,22 +1658,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920408</v>
+        <v>22330051920369</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1624,22 +1681,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920130</v>
+        <v>22330051920256</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1647,22 +1704,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>18330051920377</v>
+        <v>21330051920396</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1670,24 +1727,185 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
+        <v>22330051920265</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920272</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920274</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920298</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920408</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920130</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>18330051920377</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
         <v>21330051920148</v>
       </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" t="s">
         <v>9</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F29" t="s">
         <v>15</v>
       </c>
-      <c r="G22">
+      <c r="G29">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
   <si>
     <t>Mat</t>
   </si>
@@ -91,72 +91,75 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
     <t>JOSE</t>
   </si>
   <si>
@@ -202,9 +205,18 @@
     <t>CASASOLA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>GALLARDO</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>TELLEZ</t>
   </si>
   <si>
@@ -223,9 +235,6 @@
     <t>AILYN</t>
   </si>
   <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
@@ -280,10 +289,19 @@
     <t>SERGIO IVAN</t>
   </si>
   <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
     <t>ALDO</t>
   </si>
   <si>
     <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
+    <t>GERMAN</t>
   </si>
   <si>
     <t>JOSE CARMELO</t>
@@ -943,16 +961,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H4">
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1138,16 +1159,16 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>67.5</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1235,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1273,10 +1294,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1296,10 +1317,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1313,16 +1334,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920404</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1336,22 +1357,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920279</v>
+        <v>22330051920291</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1359,16 +1380,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920291</v>
+        <v>22330051920412</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1382,16 +1403,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920412</v>
+        <v>22330051920307</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1405,16 +1426,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1428,16 +1449,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920419</v>
+        <v>22330051920308</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1451,16 +1472,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920308</v>
+        <v>22330051920397</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1474,16 +1495,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920397</v>
+        <v>22330051920314</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1497,22 +1518,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920314</v>
+        <v>21330051920117</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1520,22 +1541,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920117</v>
+        <v>21330051920145</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1543,39 +1564,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920145</v>
+        <v>22330051920317</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920317</v>
+        <v>22330051920421</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1589,22 +1610,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920421</v>
+        <v>22330051920238</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1612,16 +1633,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920238</v>
+        <v>22330051920242</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1635,16 +1656,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920242</v>
+        <v>22330051920369</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1658,16 +1679,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920369</v>
+        <v>22330051920256</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1681,22 +1702,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920256</v>
+        <v>21330051920396</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1704,16 +1725,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920396</v>
+        <v>22330051920265</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1727,16 +1748,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920265</v>
+        <v>22330051920411</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1753,13 +1774,13 @@
         <v>22330051920272</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1776,13 +1797,13 @@
         <v>22330051920274</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1796,22 +1817,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920298</v>
+        <v>22330051920406</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1819,22 +1840,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920408</v>
+        <v>22330051920283</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1842,22 +1863,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920130</v>
+        <v>22330051920298</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1865,22 +1886,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>18330051920377</v>
+        <v>22330051920408</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1888,24 +1909,70 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920148</v>
+        <v>21330051920130</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>18330051920377</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920148</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
         <v>15</v>
       </c>
-      <c r="G29">
+      <c r="G31">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="104">
   <si>
     <t>Mat</t>
   </si>
@@ -118,15 +118,15 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>RONZON</t>
-  </si>
-  <si>
     <t>FALFAN</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -151,6 +151,9 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>QUERO</t>
   </si>
   <si>
@@ -160,6 +163,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
@@ -175,9 +181,6 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -193,6 +196,9 @@
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -220,6 +226,9 @@
     <t>TELLEZ</t>
   </si>
   <si>
+    <t>LUIS</t>
+  </si>
+  <si>
     <t>SERRANO</t>
   </si>
   <si>
@@ -235,6 +244,9 @@
     <t>AILYN</t>
   </si>
   <si>
+    <t>MIA</t>
+  </si>
+  <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
@@ -268,15 +280,15 @@
     <t>JESUS ALEJANDRO</t>
   </si>
   <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
     <t>JOSAVIA ARIDAI</t>
   </si>
   <si>
     <t>JOCELYN</t>
   </si>
   <si>
+    <t>JARET</t>
+  </si>
+  <si>
     <t>NIDIA GABRIELA</t>
   </si>
   <si>
@@ -305,6 +317,9 @@
   </si>
   <si>
     <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>EDWIN YAMIL</t>
@@ -714,19 +729,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>76.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,10 +755,10 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>31</v>
@@ -752,7 +767,7 @@
         <v>75.61</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,19 +781,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -792,10 +807,10 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>27</v>
@@ -818,10 +833,10 @@
         <v>26</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>4</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>22</v>
@@ -830,7 +845,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -909,19 +924,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -935,10 +950,10 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -947,7 +962,7 @@
         <v>65.84999999999999</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -961,19 +976,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -987,10 +1002,10 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>22</v>
@@ -1013,10 +1028,10 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>16</v>
@@ -1025,7 +1040,7 @@
         <v>61.54</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1104,19 +1119,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1130,10 +1145,10 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -1142,7 +1157,7 @@
         <v>65.84999999999999</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1156,19 +1171,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1182,10 +1197,10 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>22</v>
@@ -1208,10 +1223,10 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>16</v>
@@ -1220,7 +1235,7 @@
         <v>61.54</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1256,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1297,7 +1312,7 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1317,10 +1332,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1334,16 +1349,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920279</v>
+        <v>22330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1357,22 +1372,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920291</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1380,16 +1395,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920412</v>
+        <v>22330051920291</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1403,16 +1418,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920307</v>
+        <v>22330051920412</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1426,16 +1441,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920419</v>
+        <v>22330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1449,16 +1464,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920308</v>
+        <v>22330051920419</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1472,16 +1487,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920397</v>
+        <v>22330051920308</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1495,16 +1510,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920314</v>
+        <v>22330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1518,22 +1533,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920117</v>
+        <v>22330051920314</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1541,22 +1556,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920145</v>
+        <v>21330051920117</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1564,39 +1579,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920317</v>
+        <v>21330051920145</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920421</v>
+        <v>22330051920317</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1613,13 +1628,13 @@
         <v>22330051920238</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1636,13 +1651,13 @@
         <v>22330051920242</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1656,16 +1671,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920369</v>
+        <v>22330051920357</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1679,16 +1694,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920256</v>
+        <v>22330051920369</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1702,22 +1717,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920396</v>
+        <v>22330051920256</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1725,16 +1740,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920265</v>
+        <v>21330051920396</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1748,16 +1763,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920411</v>
+        <v>22330051920265</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1771,16 +1786,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920272</v>
+        <v>22330051920411</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1794,16 +1809,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920274</v>
+        <v>22330051920272</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1817,16 +1832,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920406</v>
+        <v>22330051920274</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1840,16 +1855,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920283</v>
+        <v>22330051920406</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1863,22 +1878,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920298</v>
+        <v>22330051920283</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1886,16 +1901,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920408</v>
+        <v>22330051920298</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1909,22 +1924,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920130</v>
+        <v>22330051920408</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1932,22 +1947,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>18330051920377</v>
+        <v>22330051920373</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1955,24 +1970,70 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920148</v>
+        <v>21330051920130</v>
       </c>
       <c r="B31" t="s">
         <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>18330051920377</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920148</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
         <v>15</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="111">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>MEDINA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -115,6 +118,15 @@
     <t>ENCARNACION</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
@@ -124,9 +136,6 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -136,9 +145,6 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -187,6 +196,12 @@
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
@@ -196,9 +211,6 @@
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -220,9 +232,6 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>TELLEZ</t>
   </si>
   <si>
@@ -241,6 +250,9 @@
     <t>VALERIA DANAY</t>
   </si>
   <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
     <t>AILYN</t>
   </si>
   <si>
@@ -272,6 +284,15 @@
   </si>
   <si>
     <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
   </si>
   <si>
     <t>ALEXIS ISAI</t>
@@ -1271,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1309,10 +1330,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1326,22 +1347,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>22330051920218</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1349,22 +1370,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920263</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1372,16 +1393,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920279</v>
+        <v>22330051920263</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1395,22 +1416,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920291</v>
+        <v>22330051920279</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1418,16 +1439,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920412</v>
+        <v>22330051920291</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1441,16 +1462,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920307</v>
+        <v>22330051920412</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1464,16 +1485,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920419</v>
+        <v>22330051920307</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1487,16 +1508,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920308</v>
+        <v>22330051920419</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1510,16 +1531,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920397</v>
+        <v>22330051920308</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1533,16 +1554,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920314</v>
+        <v>22330051920397</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1556,22 +1577,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920117</v>
+        <v>22330051920314</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1579,22 +1600,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920145</v>
+        <v>21330051920117</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1602,114 +1623,114 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920317</v>
+        <v>21330051920120</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920238</v>
+        <v>21330051920140</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920242</v>
+        <v>21330051920141</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920357</v>
+        <v>21330051920145</v>
       </c>
       <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920369</v>
+        <v>22330051920317</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1717,16 +1738,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920256</v>
+        <v>22330051920238</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1740,22 +1761,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920396</v>
+        <v>22330051920242</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1763,22 +1784,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920265</v>
+        <v>22330051920357</v>
       </c>
       <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
         <v>34</v>
       </c>
-      <c r="C22" t="s">
-        <v>63</v>
-      </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1786,22 +1807,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920411</v>
+        <v>22330051920369</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
         <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1809,22 +1830,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920272</v>
+        <v>22330051920256</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1832,16 +1853,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920274</v>
+        <v>21330051920396</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1855,16 +1876,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920406</v>
+        <v>22330051920265</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1878,16 +1899,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920283</v>
+        <v>22330051920411</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1901,22 +1922,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920298</v>
+        <v>22330051920272</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1924,22 +1945,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920408</v>
+        <v>22330051920274</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1947,22 +1968,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920373</v>
+        <v>22330051920406</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1970,22 +1991,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920130</v>
+        <v>22330051920283</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1993,22 +2014,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>18330051920377</v>
+        <v>22330051920298</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2016,24 +2037,116 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
+        <v>22330051920408</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>22330051920373</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>18330051920377</v>
+      </c>
+      <c r="B36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>109</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
         <v>21330051920148</v>
       </c>
-      <c r="B33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" t="s">
         <v>9</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F37" t="s">
         <v>15</v>
       </c>
-      <c r="G33">
+      <c r="G37">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="118">
   <si>
     <t>Mat</t>
   </si>
@@ -91,12 +91,24 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
@@ -121,13 +133,16 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ORTEGA</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>FALFAN</t>
@@ -136,15 +151,9 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
@@ -169,18 +178,21 @@
     <t>ESPARZA</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
     <t>JOSE</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -199,9 +211,15 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
@@ -211,15 +229,9 @@
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>TETLACTLE</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
     <t>CASASOLA</t>
   </si>
   <si>
@@ -253,12 +265,24 @@
     <t>ANGELES VALERIA</t>
   </si>
   <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
     <t>AILYN</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
@@ -289,6 +313,9 @@
     <t>NATALIE</t>
   </si>
   <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
     <t>MILKA SARAY</t>
   </si>
   <si>
@@ -298,6 +325,9 @@
     <t>ALEXIS ISAI</t>
   </si>
   <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
     <t>JESUS ALEJANDRO</t>
   </si>
   <si>
@@ -310,15 +340,9 @@
     <t>JARET</t>
   </si>
   <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
     <t>JONATHAN</t>
   </si>
   <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
@@ -326,9 +350,6 @@
   </si>
   <si>
     <t>ALDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
   </si>
   <si>
     <t>JULISSA</t>
@@ -1292,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1330,10 +1351,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1353,10 +1374,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1370,16 +1391,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920369</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1393,22 +1414,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920263</v>
+        <v>22330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1416,16 +1437,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920279</v>
+        <v>21330051920396</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1439,22 +1460,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920291</v>
+        <v>22330051920263</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1462,22 +1483,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920412</v>
+        <v>22330051920274</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1485,22 +1506,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920307</v>
+        <v>22330051920281</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1508,22 +1529,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920419</v>
+        <v>22330051920279</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1531,16 +1552,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920308</v>
+        <v>22330051920291</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1554,16 +1575,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920397</v>
+        <v>22330051920412</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1577,16 +1598,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920314</v>
+        <v>22330051920307</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1600,22 +1621,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920117</v>
+        <v>22330051920419</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1623,22 +1644,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920120</v>
+        <v>22330051920308</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1646,22 +1667,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920140</v>
+        <v>22330051920397</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1669,22 +1690,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920141</v>
+        <v>22330051920314</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1692,22 +1713,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920145</v>
+        <v>21330051920117</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1715,160 +1736,160 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920317</v>
+        <v>21330051920120</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920238</v>
+        <v>21330051920135</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920242</v>
+        <v>21330051920140</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920357</v>
+        <v>21330051920141</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920369</v>
+        <v>21330051920145</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920256</v>
+        <v>21330051920147</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920396</v>
+        <v>22330051920317</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1876,22 +1897,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920265</v>
+        <v>22330051920238</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1899,22 +1920,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920411</v>
+        <v>22330051920242</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1922,22 +1943,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920272</v>
+        <v>22330051920357</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1945,22 +1966,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920274</v>
+        <v>22330051920256</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1968,16 +1989,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920406</v>
+        <v>22330051920265</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1991,16 +2012,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920283</v>
+        <v>22330051920411</v>
       </c>
       <c r="B31" t="s">
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2014,22 +2035,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920298</v>
+        <v>22330051920272</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2037,22 +2058,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920408</v>
+        <v>22330051920406</v>
       </c>
       <c r="B33" t="s">
         <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2060,22 +2081,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920373</v>
+        <v>22330051920283</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2083,22 +2104,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920130</v>
+        <v>22330051920298</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2106,22 +2127,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>18330051920377</v>
+        <v>22330051920408</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2129,24 +2150,93 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
+        <v>22330051920373</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920130</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>18330051920377</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
         <v>21330051920148</v>
       </c>
-      <c r="B37" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" t="s">
         <v>9</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F40" t="s">
         <v>15</v>
       </c>
-      <c r="G37">
+      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="123">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -145,6 +148,9 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>FALFAN</t>
   </si>
   <si>
@@ -178,6 +184,9 @@
     <t>ESPARZA</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -265,6 +274,9 @@
     <t>ANGELES VALERIA</t>
   </si>
   <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
     <t>NIDIA GABRIELA</t>
   </si>
   <si>
@@ -326,6 +338,9 @@
   </si>
   <si>
     <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>JESUS ALEJANDRO</t>
@@ -1313,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1351,10 +1366,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1374,10 +1389,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1391,16 +1406,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920369</v>
+        <v>22330051920239</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1414,16 +1429,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920366</v>
+        <v>22330051920369</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1437,22 +1452,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920396</v>
+        <v>22330051920366</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1460,16 +1475,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1483,16 +1498,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920274</v>
+        <v>22330051920263</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1506,16 +1521,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920281</v>
+        <v>22330051920274</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1529,16 +1544,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920279</v>
+        <v>22330051920281</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1552,22 +1567,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920291</v>
+        <v>22330051920279</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1575,16 +1590,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920412</v>
+        <v>22330051920291</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1598,16 +1613,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920307</v>
+        <v>22330051920412</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1621,16 +1636,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920419</v>
+        <v>22330051920307</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1644,16 +1659,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920308</v>
+        <v>22330051920419</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1667,16 +1682,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920397</v>
+        <v>22330051920308</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1690,16 +1705,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920314</v>
+        <v>22330051920397</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1713,22 +1728,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920117</v>
+        <v>22330051920314</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1736,16 +1751,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920120</v>
+        <v>21330051920117</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1759,22 +1774,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920135</v>
+        <v>21330051920120</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1782,16 +1797,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1805,16 +1820,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920141</v>
+        <v>21330051920140</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1828,16 +1843,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920145</v>
+        <v>21330051920141</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1851,16 +1866,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920147</v>
+        <v>21330051920145</v>
       </c>
       <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
         <v>41</v>
       </c>
-      <c r="C24" t="s">
-        <v>66</v>
-      </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1874,68 +1889,68 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920317</v>
+        <v>21330051920147</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920238</v>
+        <v>21330051920382</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920242</v>
+        <v>22330051920317</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1943,16 +1958,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920357</v>
+        <v>22330051920238</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1966,16 +1981,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920256</v>
+        <v>22330051920242</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1989,22 +2004,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920265</v>
+        <v>22330051920357</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2012,22 +2027,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920411</v>
+        <v>22330051920256</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2035,16 +2050,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920272</v>
+        <v>22330051920265</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2058,16 +2073,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920406</v>
+        <v>22330051920411</v>
       </c>
       <c r="B33" t="s">
         <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2081,16 +2096,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920283</v>
+        <v>22330051920272</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2104,22 +2119,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920298</v>
+        <v>22330051920406</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2127,22 +2142,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920408</v>
+        <v>22330051920283</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2150,16 +2165,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920373</v>
+        <v>22330051920298</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2173,22 +2188,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920130</v>
+        <v>22330051920408</v>
       </c>
       <c r="B38" t="s">
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2196,22 +2211,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>18330051920377</v>
+        <v>22330051920373</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2219,24 +2234,70 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920148</v>
+        <v>21330051920130</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
       <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>18330051920377</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920148</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" t="s">
         <v>15</v>
       </c>
-      <c r="G40">
+      <c r="G42">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="125">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
@@ -109,66 +112,66 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
+    <t>ELIZALDE</t>
   </si>
   <si>
     <t>PANTOJA</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -202,57 +205,57 @@
     <t>JOSE</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>TELLEZ</t>
   </si>
   <si>
@@ -268,6 +271,9 @@
     <t>GALICIA</t>
   </si>
   <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
     <t>VALERIA DANAY</t>
   </si>
   <si>
@@ -292,88 +298,88 @@
     <t>AGUSTIN ARTURO</t>
   </si>
   <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
     <t>MONSERRAT</t>
   </si>
   <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
+    <t>GERMAN</t>
   </si>
   <si>
     <t>MIA NOEMI</t>
   </si>
   <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
+    <t>JOSE CARMELO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
   </si>
   <si>
     <t>ANGEL FRANCISCO</t>
@@ -1328,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1360,16 +1366,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920216</v>
+        <v>22330051920362</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1383,16 +1389,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920218</v>
+        <v>22330051920216</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1406,7 +1412,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920239</v>
+        <v>22330051920218</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1415,13 +1421,13 @@
         <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1429,7 +1435,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920369</v>
+        <v>22330051920239</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1438,7 +1444,7 @@
         <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1452,7 +1458,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920366</v>
+        <v>22330051920369</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1461,7 +1467,7 @@
         <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1475,7 +1481,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920396</v>
+        <v>22330051920366</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1484,13 +1490,13 @@
         <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1498,7 +1504,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
@@ -1507,7 +1513,7 @@
         <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1521,16 +1527,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920274</v>
+        <v>22330051920263</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1544,16 +1550,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920281</v>
+        <v>22330051920274</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1570,13 +1576,13 @@
         <v>22330051920279</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1593,13 +1599,13 @@
         <v>22330051920291</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1613,16 +1619,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920412</v>
+        <v>22330051920307</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1636,16 +1642,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1659,16 +1665,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920419</v>
+        <v>22330051920397</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1682,16 +1688,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920308</v>
+        <v>22330051920314</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1705,22 +1711,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920397</v>
+        <v>21330051920117</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1728,22 +1734,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920314</v>
+        <v>21330051920120</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1751,16 +1757,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920117</v>
+        <v>21330051920391</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1774,22 +1780,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920120</v>
+        <v>21330051920135</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1797,16 +1803,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1820,16 +1826,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920140</v>
+        <v>21330051920141</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1843,16 +1849,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920141</v>
+        <v>21330051920145</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1866,16 +1872,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920145</v>
+        <v>21330051920382</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1889,68 +1895,68 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920147</v>
+        <v>22330051920317</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920382</v>
+        <v>22330051920238</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920317</v>
+        <v>22330051920242</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1958,16 +1964,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920238</v>
+        <v>22330051920357</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1981,16 +1987,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920242</v>
+        <v>22330051920256</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2004,22 +2010,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920357</v>
+        <v>22330051920265</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2027,22 +2033,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920256</v>
+        <v>22330051920411</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2050,16 +2056,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920265</v>
+        <v>22330051920272</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2073,16 +2079,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920411</v>
+        <v>22330051920406</v>
       </c>
       <c r="B33" t="s">
         <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2096,16 +2102,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920272</v>
+        <v>22330051920281</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2119,16 +2125,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920406</v>
+        <v>22330051920283</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2142,22 +2148,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920283</v>
+        <v>22330051920412</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2171,10 +2177,10 @@
         <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2188,16 +2194,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920408</v>
+        <v>22330051920308</v>
       </c>
       <c r="B38" t="s">
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2211,7 +2217,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>22330051920373</v>
+        <v>22330051920408</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
@@ -2220,7 +2226,7 @@
         <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2234,7 +2240,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920130</v>
+        <v>22330051920373</v>
       </c>
       <c r="B40" t="s">
         <v>52</v>
@@ -2243,13 +2249,13 @@
         <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2257,7 +2263,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>18330051920377</v>
+        <v>21330051920130</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
@@ -2266,7 +2272,7 @@
         <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -2280,24 +2286,47 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920148</v>
+        <v>18330051920377</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
         <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
       </c>
       <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
         <v>15</v>
       </c>
-      <c r="G42">
+      <c r="G43">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="126">
   <si>
     <t>Mat</t>
   </si>
@@ -94,10 +94,13 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>HUERTA</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -109,19 +112,67 @@
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>ATLAHUA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ENCARNACION</t>
@@ -130,54 +181,6 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
@@ -187,10 +190,13 @@
     <t>ESPARZA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>MENDEZ</t>
   </si>
   <si>
     <t>FLORES</t>
@@ -202,16 +208,58 @@
     <t>FIERROS</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>LUIS</t>
   </si>
   <si>
     <t>MONTALVO</t>
@@ -220,48 +268,6 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
     <t>SERRANO</t>
   </si>
   <si>
@@ -280,10 +286,13 @@
     <t>ANGELES VALERIA</t>
   </si>
   <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
-    <t>NIDIA GABRIELA</t>
+    <t>JOCELYN</t>
   </si>
   <si>
     <t>AILYN</t>
@@ -295,7 +304,64 @@
     <t>MIA</t>
   </si>
   <si>
-    <t>AGUSTIN ARTURO</t>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>GERMAN</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
   </si>
   <si>
     <t>HECTOR MISAEL</t>
@@ -304,85 +370,22 @@
     <t>EFRAIN DE JESUS</t>
   </si>
   <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>DIANA IRAIS</t>
   </si>
   <si>
     <t>NATALIE</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>EDWIN YAMIL</t>
@@ -1372,10 +1375,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1395,10 +1398,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1418,10 +1421,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1435,16 +1438,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920239</v>
+        <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1458,16 +1461,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920369</v>
+        <v>22330051920239</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1481,16 +1484,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920366</v>
+        <v>22330051920242</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1504,22 +1507,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920396</v>
+        <v>22330051920366</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1527,16 +1530,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1550,16 +1553,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920274</v>
+        <v>22330051920263</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1573,22 +1576,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920279</v>
+        <v>22330051920307</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1596,16 +1599,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920291</v>
+        <v>22330051920419</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1619,16 +1622,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920307</v>
+        <v>22330051920397</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1642,16 +1645,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920419</v>
+        <v>22330051920314</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1665,22 +1668,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920397</v>
+        <v>21330051920391</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1688,22 +1691,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920314</v>
+        <v>21330051920133</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1711,22 +1714,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920117</v>
+        <v>21330051920135</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1734,22 +1737,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920120</v>
+        <v>21330051920140</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1757,22 +1760,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920391</v>
+        <v>21330051920141</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1780,16 +1783,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1803,16 +1806,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920140</v>
+        <v>21330051920382</v>
       </c>
       <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1826,7 +1829,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920141</v>
+        <v>22330051920317</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
@@ -1835,82 +1838,82 @@
         <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920145</v>
+        <v>22330051920238</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920382</v>
+        <v>22330051920357</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920317</v>
+        <v>22330051920256</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1918,22 +1921,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920238</v>
+        <v>22330051920261</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1941,22 +1944,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920242</v>
+        <v>22330051920265</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1964,22 +1967,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920357</v>
+        <v>22330051920411</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1987,22 +1990,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920256</v>
+        <v>22330051920272</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2010,16 +2013,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920265</v>
+        <v>22330051920406</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2033,16 +2036,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920411</v>
+        <v>22330051920279</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2056,16 +2059,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920272</v>
+        <v>22330051920283</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2079,22 +2082,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920406</v>
+        <v>22330051920291</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2102,22 +2105,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920281</v>
+        <v>22330051920412</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2125,22 +2128,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920283</v>
+        <v>22330051920298</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2148,16 +2151,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920412</v>
+        <v>22330051920308</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2171,16 +2174,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920298</v>
+        <v>22330051920408</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2194,13 +2197,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920308</v>
+        <v>22330051920373</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
         <v>120</v>
@@ -2217,22 +2220,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>22330051920408</v>
+        <v>21330051920117</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2240,22 +2243,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>22330051920373</v>
+        <v>21330051920120</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2266,13 +2269,13 @@
         <v>21330051920130</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -2289,13 +2292,13 @@
         <v>18330051920377</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -2312,13 +2315,13 @@
         <v>21330051920148</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -94,36 +94,6 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -145,123 +115,42 @@
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>ESPARZA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>NAJERA</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -286,36 +175,6 @@
     <t>ANGELES VALERIA</t>
   </si>
   <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
     <t>LOGAN FRANCISCO</t>
   </si>
   <si>
@@ -338,48 +197,6 @@
   </si>
   <si>
     <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>DIANA IRAIS</t>
@@ -1214,16 +1031,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>65.84999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1240,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>62.5</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1266,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>61.11</v>
+        <v>97.22</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1337,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1375,10 +1192,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1398,10 +1215,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
         <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1421,10 +1238,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1438,22 +1255,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920236</v>
+        <v>21330051920391</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1461,22 +1278,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920239</v>
+        <v>21330051920133</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1484,22 +1301,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920242</v>
+        <v>21330051920135</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1507,22 +1324,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920366</v>
+        <v>21330051920140</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1530,22 +1347,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920396</v>
+        <v>21330051920141</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1553,22 +1370,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920263</v>
+        <v>21330051920145</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1576,22 +1393,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920307</v>
+        <v>21330051920382</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1599,85 +1416,85 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920419</v>
+        <v>22330051920317</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920397</v>
+        <v>21330051920117</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920314</v>
+        <v>21330051920120</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920391</v>
+        <v>21330051920130</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1686,21 +1503,21 @@
         <v>14</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920133</v>
+        <v>18330051920377</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1709,21 +1526,21 @@
         <v>14</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920135</v>
+        <v>21330051920148</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1732,604 +1549,6 @@
         <v>15</v>
       </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920140</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920141</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920145</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920382</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920317</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920238</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920357</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920256</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920261</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920265</v>
-      </c>
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920411</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920272</v>
-      </c>
-      <c r="B29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920406</v>
-      </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920279</v>
-      </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920283</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920291</v>
-      </c>
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920412</v>
-      </c>
-      <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920298</v>
-      </c>
-      <c r="B35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920308</v>
-      </c>
-      <c r="B36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920408</v>
-      </c>
-      <c r="B37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920373</v>
-      </c>
-      <c r="B38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920117</v>
-      </c>
-      <c r="B39" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" t="s">
-        <v>121</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920120</v>
-      </c>
-      <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920130</v>
-      </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>18330051920377</v>
-      </c>
-      <c r="B42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920148</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -85,21 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -115,30 +100,9 @@
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -148,39 +112,9 @@
     <t>NAJERA</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
     <t>PEDRO ANGEL</t>
   </si>
   <si>
@@ -194,21 +128,6 @@
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
   </si>
   <si>
     <t>ROGELIO</t>
@@ -1005,16 +924,16 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>76.47</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1109,16 +1028,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>61.54</v>
+        <v>92.31</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1154,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,22 +1105,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1209,22 +1128,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920216</v>
+        <v>21330051920140</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1232,22 +1151,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920218</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1255,22 +1174,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920391</v>
+        <v>21330051920145</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1278,22 +1197,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920133</v>
+        <v>21330051920382</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1301,16 +1220,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920135</v>
+        <v>21330051920148</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1319,236 +1238,6 @@
         <v>15</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920140</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920141</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920382</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920317</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920117</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920120</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920130</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>18330051920377</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -85,52 +85,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
   </si>
 </sst>
 </file>
@@ -1054,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>46.67</v>
+        <v>73.33</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1073,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1105,16 +1072,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1128,16 +1095,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1147,98 +1114,6 @@
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920141</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920145</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920382</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920148</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
   </si>
   <si>
     <t>ALEXIS ISAI</t>
@@ -1040,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,16 +1081,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920147</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1095,16 +1104,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920382</v>
+        <v>21330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1113,7 +1122,30 @@
         <v>15</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920382</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20221.xlsx
@@ -507,10 +507,10 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>28</v>
@@ -702,10 +702,10 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -897,10 +897,10 @@
         <v>34</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>1</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>33</v>
